--- a/artfynd/S 677-2025 artfynd.xlsx
+++ b/artfynd/S 677-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AZ111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103198604</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68176693</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67299228</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57033801</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104230095</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14431554</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78671683</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1587,6 +1627,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90313295</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1684,6 +1729,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62085991</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1781,6 +1831,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57197820</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,6 +1933,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431625</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1995,6 +2055,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126870367</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2097,6 +2162,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126666346</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2199,6 +2269,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126870396</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2301,6 +2376,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126666643</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2403,6 +2483,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126666644</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2505,6 +2590,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126870633</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2616,6 +2706,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129782067</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2722,6 +2817,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129783051</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2828,6 +2928,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129783052</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2934,6 +3039,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129783065</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3040,6 +3150,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129783066</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3146,6 +3261,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129782904</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3252,6 +3372,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129782288</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3350,6 +3475,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126870392</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3475,6 +3605,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370785</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3600,6 +3735,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370792</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3707,6 +3847,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118171602</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3809,6 +3954,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118171751</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3915,6 +4065,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129783064</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4040,6 +4195,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370782</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4165,6 +4325,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370790</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4290,6 +4455,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370780</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4415,6 +4585,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370791</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4540,6 +4715,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370786</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4665,6 +4845,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370794</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4790,6 +4975,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370781</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4892,6 +5082,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118171604</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4994,6 +5189,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118171760</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5106,6 +5306,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125979817</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5231,6 +5436,11 @@
       <c r="AY42" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4139774</t>
         </is>
       </c>
     </row>
@@ -5347,6 +5557,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56713043</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5444,6 +5659,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57197812</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5541,6 +5761,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431571</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5638,6 +5863,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431710</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5759,6 +5989,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14448843</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5865,6 +6100,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57040251</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5972,6 +6212,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62732900</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6098,6 +6343,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15007073</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6205,6 +6455,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57237856</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6316,6 +6571,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62193885</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6413,6 +6673,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62193886</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6515,6 +6780,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62127065</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6617,6 +6887,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62536638</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6722,6 +6997,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124885856</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6828,6 +7108,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124884229</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6947,6 +7232,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118095918</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7072,6 +7362,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476425</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7200,6 +7495,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932558</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7328,6 +7628,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932559</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7456,6 +7761,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932567</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7584,6 +7894,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932568</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7701,6 +8016,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108586581</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7818,6 +8138,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108588657</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7937,6 +8262,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108705584</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8046,6 +8376,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116038032</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8148,6 +8483,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158228</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8268,6 +8608,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805707</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8388,6 +8733,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805713</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8518,6 +8868,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893403</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8648,6 +9003,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893404</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8778,6 +9138,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893405</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8908,6 +9273,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893406</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9024,6 +9394,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1170590</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9121,6 +9496,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158234</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9227,6 +9607,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59870550</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9329,6 +9714,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59870551</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9431,6 +9821,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62124150</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9533,6 +9928,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62057622</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9631,6 +10031,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62085379</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9733,6 +10138,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62531178</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9840,6 +10250,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62505215</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9947,6 +10362,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254157</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10054,6 +10474,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254158</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10161,6 +10586,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254159</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10258,6 +10688,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114280905</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10355,6 +10790,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114280906</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10462,6 +10902,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253819</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10573,6 +11018,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254044</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10680,6 +11130,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254163</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10787,6 +11242,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254164</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10889,6 +11349,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62123691</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10986,6 +11451,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62303391</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11083,6 +11553,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62082557</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11185,6 +11660,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62082560</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11292,6 +11772,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62505206</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11389,6 +11874,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58219870</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11486,6 +11976,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431594</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11606,6 +12101,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045762</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11734,6 +12234,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045761</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11853,6 +12358,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045759</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11972,6 +12482,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045758</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12096,6 +12611,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045764</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12216,6 +12736,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045763</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12335,6 +12860,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045770</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12454,6 +12984,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045772</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12573,6 +13108,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045767</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12702,6 +13242,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118216554</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12831,6 +13376,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118217261</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12928,8 +13478,125 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431666</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>